--- a/fødseldag.xlsx
+++ b/fødseldag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjsto\Documents\Git\fdag\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F540C34F-D2A8-4A01-B1D8-C62BA3313AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A8111D-CE01-442B-BD89-16706878D4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="0" windowWidth="19180" windowHeight="11370" xr2:uid="{1D7C1D20-DE9D-4945-9F41-96F6CAF10542}"/>
+    <workbookView xWindow="20" yWindow="1160" windowWidth="19180" windowHeight="6000" xr2:uid="{1D7C1D20-DE9D-4945-9F41-96F6CAF10542}"/>
   </bookViews>
   <sheets>
     <sheet name="fødseldag" sheetId="1" r:id="rId1"/>
@@ -1360,7 +1360,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="1">
-        <v>36299</v>
+        <v>36290</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
@@ -1456,7 +1456,7 @@
         <v>49</v>
       </c>
       <c r="B52" s="1">
-        <v>35279</v>
+        <v>22860</v>
       </c>
     </row>
   </sheetData>
